--- a/site/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Provisioning</t>
+          <t>Application Setting</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -605,19 +605,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
+          <t>h_01KQYN6D4BSJ9ABC36RXC2W0NX</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KQYN6D4BSJ9ABC36RXC2W0NX</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Directory</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,19 +627,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Directory Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,63 +649,63 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>h_01KQYY6C1XZDQBYVJR1A267TC6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KQYY6C1XZDQBYVJR1A267TC6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Application Configuration</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>h_01K04AVZNHW4RD086HGMDCJSM6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04AVZNHW4RD086HGMDCJSM6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Global Settings</t>
+          <t>Groups Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01K04AVZNHW4RD086HGMDCJSM6</t>
+          <t>h_01KQYY3KS9RVC41JZNCFTDB7W6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04AVZNHW4RD086HGMDCJSM6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KQYY3KS9RVC41JZNCFTDB7W6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Candidates Group Configuration</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,164 +715,274 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KQYY5BYS218GEN8QJGBZ8PA1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KQYY5BYS218GEN8QJGBZ8PA1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Global Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KQYY6C1YRWSPC4CG2PD2S95F</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KQYY6C1YRWSPC4CG2PD2S95F</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,73 +727,73 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Manage Candidate - Entra ID</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>h_01KR0P5K5CB2W1KZKPK5XAY6W8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0P5K5CB2W1KZKPK5XAY6W8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Account Correlation Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>h_01KR0P5K5C58VT2NA0E82V536W</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0P5K5C58VT2NA0E82V536W</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Account Activation Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>h_01KR0P5K5CW9PZXM41AKX8KYPQ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0P5K5CW9PZXM41AKX8KYPQ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Global Settings</t>
+          <t>Account Update Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KQYY6C1YRWSPC4CG2PD2S95F</t>
+          <t>h_01KR0P5K5C239BD2RAVFHANG8S</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KQYY6C1YRWSPC4CG2PD2S95F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0P5K5C239BD2RAVFHANG8S</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Account Deactivation Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KR0P5K5CCPY4K3TXN0WZAQF4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0P5K5CCPY4K3TXN0WZAQF4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Attribute Mapping</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KR0P5K5DFVJ82375NXJF0Z2M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0P5K5DFVJ82375NXJF0Z2M</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,120 +869,274 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Access Rules</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Naming Policy</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KR0NT88RR9ZVGAK5VJ4PZ6GC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0NT88RR9ZVGAK5VJ4PZ6GC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Global Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KQYY6C1YRWSPC4CG2PD2S95F</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KQYY6C1YRWSPC4CG2PD2S95F</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KR0P5K5CB2W1KZKPK5XAY6W8</t>
+          <t>h_01KR10EFV0M46YQF4TVJD1ZMHK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0P5K5CB2W1KZKPK5XAY6W8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR10EFV0M46YQF4TVJD1ZMHK</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KR0P5K5C58VT2NA0E82V536W</t>
+          <t>h_01KR10EFV0D8MHANTHJAKEX4AV</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0P5K5C58VT2NA0E82V536W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR10EFV0D8MHANTHJAKEX4AV</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KR0P5K5CW9PZXM41AKX8KYPQ</t>
+          <t>h_01KR10EFV01339J55KPXQSZZXS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0P5K5CW9PZXM41AKX8KYPQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR10EFV01339J55KPXQSZZXS</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KR0P5K5C239BD2RAVFHANG8S</t>
+          <t>h_01KR10EFV06RK3MCFMC9YYPJ75</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0P5K5C239BD2RAVFHANG8S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR10EFV06RK3MCFMC9YYPJ75</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KR0P5K5CCPY4K3TXN0WZAQF4</t>
+          <t>h_01KR10EFV0QYVVCSMHPQPZKTHS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0P5K5CCPY4K3TXN0WZAQF4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR10EFV0QYVVCSMHPQPZKTHS</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KR0P5K5DFVJ82375NXJF0Z2M</t>
+          <t>h_01KR10EFV0EFQN7YY3QM76ACXC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0P5K5DFVJ82375NXJF0Z2M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR10EFV0EFQN7YY3QM76ACXC</t>
         </is>
       </c>
     </row>
@@ -903,29 +903,29 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Naming Policy</t>
+          <t>Candidate Group Assignment Rule</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>h_01KR0VJPFHX7FCP99M5SQE5C24</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0VJPFHX7FCP99M5SQE5C24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Naming Policy</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KR0NT88RR9ZVGAK5VJ4PZ6GC</t>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0NT88RR9ZVGAK5VJ4PZ6GC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Global Settings</t>
+          <t>Naming Policy Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KQYY6C1YRWSPC4CG2PD2S95F</t>
+          <t>h_01KR0VMFH135WCBDQWC21SZ567</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KQYY6C1YRWSPC4CG2PD2S95F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0VMFH135WCBDQWC21SZ567</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Generate UserPrincipalName (UPN)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KR0VMJEVH5XWEZBW4461R0S4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0VMJEVH5XWEZBW4461R0S4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Generate Email</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,63 +1001,63 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KR0VMNR1JFM0NDD2AT8FN9HB</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0VMNR1JFM0NDD2AT8FN9HB</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01KR0NT88RR9ZVGAK5VJ4PZ6GC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0NT88RR9ZVGAK5VJ4PZ6GC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Password Policy Configuration</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01KR0XFA9WFHWRHXVD8CP16XR8</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0XFA9WFHWRHXVD8CP16XR8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,76 +1067,318 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KQYY6C1YRWSPC4CG2PD2S95F</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KQYY6C1YRWSPC4CG2PD2S95F</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Advance Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KN47NYDZ014D07BNJKKQFDED</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KN47NYDZ014D07BNJKKQFDED</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Operational Settings Definition</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01KN3Q8QVV3ACYFE8R1W6QS4ZA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KN3Q8QVV3ACYFE8R1W6QS4ZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Notification Center</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01KR10EFV059DKZAPPYQA25CG1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR10EFV059DKZAPPYQA25CG1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Template Library</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01KN1AVFK47V9644J22EQEDVZE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KN1AVFK47V9644J22EQEDVZE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01KR0ZVV0BZGY9W4A93SASTK7N</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0ZVV0BZGY9W4A93SASTK7N</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01KN1AVMW81679JNM3NZGGKJAY</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KN1AVMW81679JNM3NZGGKJAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Define Notification Report Configuration</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01KR0ZWCV3GAR4R4Q42P8EPPYS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR0ZWCV3GAR4R4Q42P8EPPYS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Define Notification Configuration</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01KR10CG8DVP9DB8HKBKYF76T8</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KR10CG8DVP9DB8HKBKYF76T8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-API-Central-Entra-ID-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
